--- a/outputs/daily/hr_rankings_2026-07-24_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-24_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.3</v>
+        <v>70.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>61.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>58.8</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S5" t="n">
         <v>86.40000000000001</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57.6</v>
+        <v>55.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>30.5</v>
       </c>
       <c r="R6" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.6</v>
+        <v>53.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S7" t="n">
         <v>64.3</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>30.5</v>
       </c>
       <c r="R8" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>30.5</v>
       </c>
       <c r="R9" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>30.5</v>
       </c>
       <c r="R12" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>30.5</v>
       </c>
       <c r="R13" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.1</v>
+        <v>41.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.4</v>
+        <v>40.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>30.5</v>
       </c>
       <c r="R15" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>30.5</v>
       </c>
       <c r="R16" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>30.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.3</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>29.3</v>
       </c>
       <c r="R19" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.3</v>
+        <v>70.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>61.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>58.8</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S5" t="n">
         <v>86.40000000000001</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57.6</v>
+        <v>55.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>30.5</v>
       </c>
       <c r="R6" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.6</v>
+        <v>53.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S7" t="n">
         <v>64.3</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>30.5</v>
       </c>
       <c r="R8" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>30.5</v>
       </c>
       <c r="R9" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>30.5</v>
       </c>
       <c r="R12" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>30.5</v>
       </c>
       <c r="R13" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.1</v>
+        <v>41.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.4</v>
+        <v>40.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>30.5</v>
       </c>
       <c r="R15" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>30.5</v>
       </c>
       <c r="R16" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>30.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.3</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>29.3</v>
       </c>
       <c r="R19" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
